--- a/data/polymer_gost_registry.xlsx
+++ b/data/polymer_gost_registry.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="1" max="1"/>
@@ -440,7 +440,7 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="28" customWidth="1" min="9" max="9"/>
     <col width="33" customWidth="1" min="10" max="10"/>
-    <col width="35" customWidth="1" min="11" max="11"/>
+    <col width="43" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1522,7 +1522,6 @@
           <t>04.05.2026</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Вынесен на публичное обсуждение</t>
@@ -1538,7 +1537,6 @@
           <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=247ce99c-2fcd-47a1-b6e1-308775810d05</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1581,7 +1579,6 @@
           <t>05.05.2026</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Вынесен на публичное обсуждение</t>
@@ -1597,7 +1594,6 @@
           <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=0b96395c-d423-4ee9-8a98-40c361e60237</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1640,7 +1636,6 @@
           <t>07.05.2026</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Вынесен на публичное обсуждение</t>
@@ -1656,7 +1651,360 @@
           <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=cf65a7de-885e-42c0-8300-d850f016c4d2</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>7a882e40-4766-4ca4-8141-2db96103b8e7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ГОСТ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Трубопроводы из пластмасс. Метод определения стойкости узлов соединений труба/труба или труба/фитинг к растягивающей нагрузке</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.5.241-2.109.26</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ТК 241 Трубы, фитинги, и другие изделия из пластмасс, методы испытаний</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Группа ПОЛИПЛАСТИК</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Вынесен на публичное обсуждение</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>пластмасс, пластик</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=7a882e40-4766-4ca4-8141-2db96103b8e7</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>372be503-ef03-47fe-8c5e-96d08b4c9377</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ГОСТ</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Трубы из непластифицированного поливинилхлорида (НПВХ). Стойкость к воздействию дихлорметана при заданной температуре (ДХМ). Метод испытания</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.5.241-2.113.26</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ТК 241 Трубы, фитинги, и другие изделия из пластмасс, методы испытаний</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Группа ПОЛИПЛАСТИК</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Вынесен на публичное обсуждение</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>пластмасс, пластик, пвх</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=372be503-ef03-47fe-8c5e-96d08b4c9377</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>8d68b936-b7bb-4135-ac23-7e199439d894</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ГОСТ</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Трубопроводы безнапорные из пластмасс. Метод испытания на стойкость к циклическому изменению температуры</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.5.241-2.115.26</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ТК 241 Трубы, фитинги, и другие изделия из пластмасс, методы испытаний</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Группа ПОЛИПЛАСТИК</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Вынесен на публичное обсуждение</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>пластмасс, пластик</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=8d68b936-b7bb-4135-ac23-7e199439d894</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>a87622b3-5b28-4533-aee9-8ff1c32856e6</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ГОСТ</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Трубопроводы из пластмасс. Раструбные соединения с эластомерным уплотнительным кольцом для напорных труб из термопластов. Метод испытания на герметичность при отрицательном давлении и угловом смещении</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.5.241-2.112.26</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ТК 241 Трубы, фитинги, и другие изделия из пластмасс, методы испытаний</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Группа ПОЛИПЛАСТИК</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Вынесен на публичное обсуждение</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>пластмасс, пластик, термопласт, эластомер</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=a87622b3-5b28-4533-aee9-8ff1c32856e6</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>970817ab-978d-426a-a454-a93c3607c7a1</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ГОСТ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Трубопроводы из пластмасс. Узлы и соединения для напорных труб из термопластов несущие и не несущие торцевую нагрузку. Метод испытания на долговременную герметичность под действием внутреннего давления воды</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.5.241-2.108.26</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ТК 241 Трубы, фитинги, и другие изделия из пластмасс, методы испытаний</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Группа ПОЛИПЛАСТИК</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>20.04.2026</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Вынесен на публичное обсуждение</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>пластмасс, пластик, термопласт</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=970817ab-978d-426a-a454-a93c3607c7a1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bfcc90d2-b53e-4d7d-8247-605ebbf5b7e9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>13.05.2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ГОСТ</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Трубопроводы из пластмасс для систем отвода почвенных и сточных вод, расположенные внутри зданий. Метод испытания соединений на воздухопроницаемость</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.5.241-2.110.26</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ТК 241 Трубы, фитинги, и другие изделия из пластмасс, методы испытаний</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Группа ПОЛИПЛАСТИК</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>28.04.2026</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Вынесен на публичное обсуждение</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>пластмасс, пластик</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=bfcc90d2-b53e-4d7d-8247-605ebbf5b7e9</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/polymer_gost_registry.xlsx
+++ b/data/polymer_gost_registry.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="13" customWidth="1" min="1" max="1"/>
@@ -1693,7 +1693,6 @@
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Вынесен на публичное обсуждение</t>
@@ -1709,7 +1708,6 @@
           <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=7a882e40-4766-4ca4-8141-2db96103b8e7</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1752,7 +1750,6 @@
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Вынесен на публичное обсуждение</t>
@@ -1768,7 +1765,6 @@
           <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=372be503-ef03-47fe-8c5e-96d08b4c9377</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1811,7 +1807,6 @@
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Вынесен на публичное обсуждение</t>
@@ -1827,7 +1822,6 @@
           <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=8d68b936-b7bb-4135-ac23-7e199439d894</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1870,7 +1864,6 @@
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Вынесен на публичное обсуждение</t>
@@ -1886,7 +1879,6 @@
           <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=a87622b3-5b28-4533-aee9-8ff1c32856e6</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1929,7 +1921,6 @@
           <t>20.04.2026</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Вынесен на публичное обсуждение</t>
@@ -1945,7 +1936,6 @@
           <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=970817ab-978d-426a-a454-a93c3607c7a1</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1988,7 +1978,6 @@
           <t>28.04.2026</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Вынесен на публичное обсуждение</t>
@@ -2004,7 +1993,65 @@
           <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=bfcc90d2-b53e-4d7d-8247-605ebbf5b7e9</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>23104431-8dd9-4da5-8b10-e05d9f70dd5d</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ГОСТ</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Этикетки термоусадочные легкосъемные для бутылок из полиэтилентерефталата. Критерии проектирования и методы испытаний</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.14.223-2.108.26</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ТК 223 Упаковка</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ООО «Компания ЕвроБалт»</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>14.05.2026</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Вынесен на публичное обсуждение</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>полиэтилен</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://fgis.gost.ru/share/page/rsprs/nds-details?uuid=23104431-8dd9-4da5-8b10-e05d9f70dd5d</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
